--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N202_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N202_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.486862518132701</v>
+        <v>0.8916151591965639</v>
       </c>
       <c r="D2" t="n">
-        <v>6.838569462156453</v>
+        <v>1.111267537600424</v>
       </c>
       <c r="E2" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F2" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.985521759597312</v>
+        <v>0.9726472859345633</v>
       </c>
       <c r="D3" t="n">
-        <v>5.275725379866277</v>
+        <v>0.85730537422827</v>
       </c>
       <c r="E3" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F3" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.88688042764871</v>
+        <v>4.694118069492915</v>
       </c>
       <c r="D4" t="n">
-        <v>28.17886023022163</v>
+        <v>4.579064787411014</v>
       </c>
       <c r="E4" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F4" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.08415519865884</v>
+        <v>2.126175219782062</v>
       </c>
       <c r="D5" t="n">
-        <v>11.10781781463287</v>
+        <v>1.805020394877842</v>
       </c>
       <c r="E5" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F5" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.7637106544873</v>
+        <v>6.949102981354187</v>
       </c>
       <c r="D6" t="n">
-        <v>30.09983611144091</v>
+        <v>4.891223368109149</v>
       </c>
       <c r="E6" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F6" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.37339373080488</v>
+        <v>6.885676481255793</v>
       </c>
       <c r="D7" t="n">
-        <v>41.04668299514593</v>
+        <v>6.670085986711213</v>
       </c>
       <c r="E7" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F7" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79922422098159</v>
+        <v>4.842373935909508</v>
       </c>
       <c r="D8" t="n">
-        <v>29.60902640149529</v>
+        <v>4.811466790242984</v>
       </c>
       <c r="E8" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F8" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.07805865376752</v>
+        <v>3.262684531237222</v>
       </c>
       <c r="D9" t="n">
-        <v>23.3351098692016</v>
+        <v>3.791955353745259</v>
       </c>
       <c r="E9" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F9" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.684272407499577</v>
+        <v>1.248694266218681</v>
       </c>
       <c r="D10" t="n">
-        <v>27.10778999804479</v>
+        <v>4.405015874682278</v>
       </c>
       <c r="E10" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F10" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>3.166120630489136</v>
+        <v>0.5144946024544846</v>
       </c>
       <c r="D11" t="n">
-        <v>4.102427170464539</v>
+        <v>0.6666444152004876</v>
       </c>
       <c r="E11" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F11" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.35532903694825</v>
+        <v>6.07024096850409</v>
       </c>
       <c r="D12" t="n">
-        <v>34.77408900720302</v>
+        <v>5.650789463670492</v>
       </c>
       <c r="E12" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F12" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.06715071608973</v>
+        <v>1.798411991364581</v>
       </c>
       <c r="D13" t="n">
-        <v>11.83849664628363</v>
+        <v>1.92375570502109</v>
       </c>
       <c r="E13" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F13" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.71694894416551</v>
+        <v>2.716504203426896</v>
       </c>
       <c r="D14" t="n">
-        <v>27.45503648829433</v>
+        <v>4.461443429347828</v>
       </c>
       <c r="E14" t="n">
-        <v>13.79505243580224</v>
+        <v>2.241696020817864</v>
       </c>
       <c r="F14" t="n">
-        <v>11.75045210580646</v>
+        <v>1.90944846719355</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
